--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -431,202 +431,202 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p_acc_fisher</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_acc_fisher</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p_prec_fisher</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_prec_fisher</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>p_rec_fisher</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_rec_fisher</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tp</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tn</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>fp</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_accuracy</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_accuracy</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_precision</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_precision</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_recall</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>fisher_p_f1</t>
+          <t>p_f1_fisher</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>fisher_adj_p_f1</t>
+          <t>adj_p_f1_fisher</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1920</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GPT-4o base</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1072</v>
+      </c>
+      <c r="F2" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2" t="n">
+        <v>213</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.8505208333333333</v>
       </c>
-      <c r="C2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>0.8834645669291339</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.7248062015503876</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.7963094393186657</v>
-      </c>
-      <c r="F2" t="n">
-        <v>561</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1072</v>
-      </c>
-      <c r="H2" t="n">
-        <v>74</v>
-      </c>
-      <c r="I2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>GPT-4o base</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0.7248062015503876</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0.7963094393186657</v>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1920</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>679</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="n">
+        <v>95</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.9244791666666666</v>
       </c>
-      <c r="C3" t="n">
+      <c r="I3" t="n">
+        <v>3.898328466426899e-13</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.16949853992807e-12</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.9314128943758574</v>
       </c>
-      <c r="D3" t="n">
+      <c r="L3" t="n">
+        <v>0.002439907431619333</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0029278889179432</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.8772609819121447</v>
       </c>
-      <c r="E3" t="n">
+      <c r="O3" t="n">
+        <v>5.298145018036324e-14</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.589443505410897e-13</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.9035262807717898</v>
-      </c>
-      <c r="F3" t="n">
-        <v>679</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1096</v>
-      </c>
-      <c r="H3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I3" t="n">
-        <v>95</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GPT-4o FT</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3.898328466426899e-13</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.16949853992807e-12</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.002439907431619333</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.0029278889179432</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.298145018036324e-14</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.589443505410897e-13</v>
       </c>
       <c r="R3" t="n">
         <v>3.389224674261126e-16</v>
@@ -636,60 +636,60 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>1920</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPT-4o QSP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>649</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1013</v>
+      </c>
+      <c r="F4" t="n">
+        <v>133</v>
+      </c>
+      <c r="G4" t="n">
+        <v>125</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.865625</v>
       </c>
-      <c r="C4" t="n">
+      <c r="I4" t="n">
+        <v>0.1953603227639657</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2930404841459485</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.829923273657289</v>
       </c>
-      <c r="D4" t="n">
+      <c r="L4" t="n">
+        <v>0.00506505316921481</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.00506505316921481</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.8385012919896641</v>
       </c>
-      <c r="E4" t="n">
+      <c r="O4" t="n">
+        <v>7.624205292144084e-08</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.524841058428817e-07</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.8341902313624678</v>
-      </c>
-      <c r="F4" t="n">
-        <v>649</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1013</v>
-      </c>
-      <c r="H4" t="n">
-        <v>133</v>
-      </c>
-      <c r="I4" t="n">
-        <v>125</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>GPT-4o QSP</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1953603227639657</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.2930404841459485</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.00506505316921481</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.00506505316921481</v>
-      </c>
-      <c r="P4" t="n">
-        <v>7.624205292144084e-08</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.524841058428817e-07</v>
       </c>
       <c r="R4" t="n">
         <v>0.008986771122068776</v>
@@ -699,107 +699,107 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1920</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B base</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>570</v>
+      </c>
+      <c r="E5" t="n">
+        <v>967</v>
+      </c>
+      <c r="F5" t="n">
+        <v>179</v>
+      </c>
+      <c r="G5" t="n">
+        <v>204</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.8005208333333333</v>
       </c>
-      <c r="C5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>0.7610146862483311</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7364341085271318</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.7485226526592252</v>
-      </c>
-      <c r="F5" t="n">
-        <v>570</v>
-      </c>
-      <c r="G5" t="n">
-        <v>967</v>
-      </c>
-      <c r="H5" t="n">
-        <v>179</v>
-      </c>
-      <c r="I5" t="n">
-        <v>204</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B base</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0.7364341085271318</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0.7485226526592252</v>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1920</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>558</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1122</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" t="n">
+        <v>216</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.875</v>
       </c>
-      <c r="C6" t="n">
+      <c r="I6" t="n">
+        <v>4.427251720459515e-10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.854503440919031e-10</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.9587628865979382</v>
       </c>
-      <c r="D6" t="n">
+      <c r="L6" t="n">
+        <v>3.737013487063362e-26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.242208092238017e-25</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.7209302325581395</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.8230088495575221</v>
-      </c>
-      <c r="F6" t="n">
-        <v>558</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1122</v>
-      </c>
-      <c r="H6" t="n">
-        <v>24</v>
-      </c>
-      <c r="I6" t="n">
-        <v>216</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B FT</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>4.427251720459515e-10</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8.854503440919031e-10</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.737013487063362e-26</v>
-      </c>
       <c r="O6" t="n">
-        <v>2.242208092238017e-25</v>
+        <v>0.5295206877188146</v>
       </c>
       <c r="P6" t="n">
         <v>0.5295206877188146</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5295206877188146</v>
+        <v>0.8230088495575221</v>
       </c>
       <c r="R6" t="n">
         <v>1.197349187707239e-06</v>
@@ -809,60 +809,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>1920</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>651</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1051</v>
+      </c>
+      <c r="F7" t="n">
+        <v>95</v>
+      </c>
+      <c r="G7" t="n">
+        <v>123</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.8864583333333333</v>
       </c>
-      <c r="C7" t="n">
+      <c r="I7" t="n">
+        <v>2.431190264859079e-13</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.16949853992807e-12</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.8726541554959786</v>
       </c>
-      <c r="D7" t="n">
+      <c r="L7" t="n">
+        <v>2.40861297013143e-08</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.22583891039429e-08</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.8410852713178295</v>
       </c>
-      <c r="E7" t="n">
+      <c r="O7" t="n">
+        <v>5.706145925940797e-07</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.559218888911194e-07</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.856578947368421</v>
-      </c>
-      <c r="F7" t="n">
-        <v>651</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1051</v>
-      </c>
-      <c r="H7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I7" t="n">
-        <v>123</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B QSP</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2.431190264859079e-13</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.16949853992807e-12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.40861297013143e-08</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7.22583891039429e-08</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.706145925940797e-07</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8.559218888911194e-07</v>
       </c>
       <c r="R7" t="n">
         <v>6.23386613068862e-14</v>
@@ -872,107 +872,107 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1920</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B base</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>534</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1011</v>
+      </c>
+      <c r="F8" t="n">
+        <v>135</v>
+      </c>
+      <c r="G8" t="n">
+        <v>240</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.8046875</v>
       </c>
-      <c r="C8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>0.7982062780269058</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.689922480620155</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.7401247401247402</v>
-      </c>
-      <c r="F8" t="n">
-        <v>534</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1011</v>
-      </c>
-      <c r="H8" t="n">
-        <v>135</v>
-      </c>
-      <c r="I8" t="n">
-        <v>240</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B base</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0.689922480620155</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>0.7401247401247402</v>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1920</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>481</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="F9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G9" t="n">
+        <v>293</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.8192708333333333</v>
       </c>
-      <c r="C9" t="n">
+      <c r="I9" t="n">
+        <v>0.2647888979234775</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.317746677508173</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.8990654205607477</v>
       </c>
-      <c r="D9" t="n">
+      <c r="L9" t="n">
+        <v>1.479867624661064e-06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.219801436991597e-06</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.6214470284237726</v>
       </c>
-      <c r="E9" t="n">
+      <c r="O9" t="n">
+        <v>0.005385384684188674</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.006462461621026408</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.7349121466768526</v>
-      </c>
-      <c r="F9" t="n">
-        <v>481</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H9" t="n">
-        <v>54</v>
-      </c>
-      <c r="I9" t="n">
-        <v>293</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B FT</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2647888979234775</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.317746677508173</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.479867624661064e-06</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.219801436991597e-06</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.005385384684188674</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.006462461621026408</v>
       </c>
       <c r="R9" t="n">
         <v>0.761529921442055</v>
@@ -982,60 +982,60 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1920</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>677</v>
+      </c>
+      <c r="E10" t="n">
+        <v>843</v>
+      </c>
+      <c r="F10" t="n">
+        <v>303</v>
+      </c>
+      <c r="G10" t="n">
+        <v>97</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="C10" t="n">
+      <c r="I10" t="n">
+        <v>0.3345656303396852</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3345656303396852</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.6908163265306122</v>
       </c>
-      <c r="D10" t="n">
+      <c r="L10" t="n">
+        <v>1.016945441861206e-06</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.033890883722412e-06</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.8746770025839793</v>
       </c>
-      <c r="E10" t="n">
+      <c r="O10" t="n">
+        <v>8.383971059840607e-19</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.030382635904364e-18</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.7719498289623716</v>
-      </c>
-      <c r="F10" t="n">
-        <v>677</v>
-      </c>
-      <c r="G10" t="n">
-        <v>843</v>
-      </c>
-      <c r="H10" t="n">
-        <v>303</v>
-      </c>
-      <c r="I10" t="n">
-        <v>97</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B QSP</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.3345656303396852</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.3345656303396852</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.016945441861206e-06</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.033890883722412e-06</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.383971059840607e-19</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.030382635904364e-18</v>
       </c>
       <c r="R10" t="n">
         <v>0.03816604437425253</v>

--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="E2" t="n">
         <v>1072</v>
@@ -549,25 +549,25 @@
         <v>74</v>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8505208333333333</v>
+        <v>0.84375</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.8834645669291339</v>
+        <v>0.8810289389067524</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.7248062015503876</v>
+        <v>0.7080103359173127</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.7963094393186657</v>
+        <v>0.7851002865329513</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="E3" t="n">
         <v>1096</v>
@@ -596,43 +596,43 @@
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9244791666666666</v>
+        <v>0.921875</v>
       </c>
       <c r="I3" t="n">
-        <v>3.898328466426899e-13</v>
+        <v>4.792162101787747e-14</v>
       </c>
       <c r="J3" t="n">
-        <v>1.16949853992807e-12</v>
+        <v>2.875297261072648e-13</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9314128943758574</v>
+        <v>0.930939226519337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002439907431619333</v>
+        <v>0.001766624481823072</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0029278889179432</v>
+        <v>0.002119949378187686</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8772609819121447</v>
+        <v>0.8708010335917312</v>
       </c>
       <c r="O3" t="n">
-        <v>5.298145018036324e-14</v>
+        <v>3.492797424219431e-15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.589443505410897e-13</v>
+        <v>2.095678454531659e-14</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9035262807717898</v>
+        <v>0.8998664886515354</v>
       </c>
       <c r="R3" t="n">
-        <v>3.389224674261126e-16</v>
+        <v>1.262293664965574e-17</v>
       </c>
       <c r="S3" t="n">
-        <v>2.033534804556676e-15</v>
+        <v>7.573761989793447e-17</v>
       </c>
     </row>
     <row r="4">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>649</v>
+        <v>625</v>
       </c>
       <c r="E4" t="n">
         <v>1013</v>
@@ -659,43 +659,43 @@
         <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.865625</v>
+        <v>0.853125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1953603227639657</v>
+        <v>0.4442744244051946</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2930404841459485</v>
+        <v>0.4442744244051946</v>
       </c>
       <c r="K4" t="n">
-        <v>0.829923273657289</v>
+        <v>0.8245382585751979</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00506505316921481</v>
+        <v>0.003920867650364704</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00506505316921481</v>
+        <v>0.003920867650364704</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8385012919896641</v>
+        <v>0.8074935400516796</v>
       </c>
       <c r="O4" t="n">
-        <v>7.624205292144084e-08</v>
+        <v>6.178810321821877e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.524841058428817e-07</v>
+        <v>1.235762064364375e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8341902313624678</v>
+        <v>0.8159268929503917</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008986771122068776</v>
+        <v>0.03710235356968906</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01348015668310316</v>
+        <v>0.05565353035453359</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="E5" t="n">
         <v>967</v>
@@ -722,25 +722,25 @@
         <v>179</v>
       </c>
       <c r="G5" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8005208333333333</v>
+        <v>0.7927083333333333</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.7610146862483311</v>
+        <v>0.7561307901907357</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.7364341085271318</v>
+        <v>0.7170542635658915</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.7485226526592252</v>
+        <v>0.7360742705570293</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="E6" t="n">
         <v>1122</v>
@@ -769,43 +769,43 @@
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H6" t="n">
-        <v>0.875</v>
+        <v>0.8723958333333334</v>
       </c>
       <c r="I6" t="n">
-        <v>4.427251720459515e-10</v>
+        <v>4.249473635866948e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>8.854503440919031e-10</v>
+        <v>8.498947271733896e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9587628865979382</v>
+        <v>0.9584055459272097</v>
       </c>
       <c r="L6" t="n">
-        <v>3.737013487063362e-26</v>
+        <v>1.362265031491502e-26</v>
       </c>
       <c r="M6" t="n">
-        <v>2.242208092238017e-25</v>
+        <v>8.173590188949014e-26</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7209302325581395</v>
+        <v>0.7144702842377261</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5295206877188146</v>
+        <v>0.9550681075602224</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5295206877188146</v>
+        <v>0.9550681075602224</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8230088495575221</v>
+        <v>0.8186528497409327</v>
       </c>
       <c r="R6" t="n">
-        <v>1.197349187707239e-06</v>
+        <v>1.439926366220674e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>2.394698375414478e-06</v>
+        <v>2.879852732441348e-07</v>
       </c>
     </row>
     <row r="7">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="E7" t="n">
         <v>1051</v>
@@ -832,43 +832,43 @@
         <v>95</v>
       </c>
       <c r="G7" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8864583333333333</v>
+        <v>0.8739583333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>2.431190264859079e-13</v>
+        <v>1.592234122283897e-11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.16949853992807e-12</v>
+        <v>4.776702366851691e-11</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8726541554959786</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="L7" t="n">
-        <v>2.40861297013143e-08</v>
+        <v>4.679050960720545e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>7.22583891039429e-08</v>
+        <v>1.403715288216164e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8410852713178295</v>
+        <v>0.810077519379845</v>
       </c>
       <c r="O7" t="n">
-        <v>5.706145925940797e-07</v>
+        <v>2.070535434355803e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>8.559218888911194e-07</v>
+        <v>3.105803151533705e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.856578947368421</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="R7" t="n">
-        <v>6.23386613068862e-14</v>
+        <v>7.823476059017284e-12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.870159839206586e-13</v>
+        <v>2.347042817705185e-11</v>
       </c>
     </row>
     <row r="8">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="E8" t="n">
         <v>1011</v>
@@ -895,25 +895,25 @@
         <v>135</v>
       </c>
       <c r="G8" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8046875</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.7982062780269058</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.689922480620155</v>
+        <v>0.6782945736434108</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.7401247401247402</v>
+        <v>0.7322175732217573</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E9" t="n">
         <v>1092</v>
@@ -942,43 +942,43 @@
         <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8192708333333333</v>
+        <v>0.815625</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2647888979234775</v>
+        <v>0.2349289652853259</v>
       </c>
       <c r="J9" t="n">
-        <v>0.317746677508173</v>
+        <v>0.281914758342391</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8990654205607477</v>
+        <v>0.8977272727272727</v>
       </c>
       <c r="L9" t="n">
-        <v>1.479867624661064e-06</v>
+        <v>1.433359763333451e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.219801436991597e-06</v>
+        <v>2.150039645000177e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6214470284237726</v>
+        <v>0.6124031007751938</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005385384684188674</v>
+        <v>0.007871184960464721</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006462461621026408</v>
+        <v>0.009445421952557665</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7349121466768526</v>
+        <v>0.7281105990783411</v>
       </c>
       <c r="R9" t="n">
-        <v>0.761529921442055</v>
+        <v>0.8293084478898946</v>
       </c>
       <c r="S9" t="n">
-        <v>0.761529921442055</v>
+        <v>0.8293084478898946</v>
       </c>
     </row>
     <row r="10">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="E10" t="n">
         <v>843</v>
@@ -1005,43 +1005,43 @@
         <v>303</v>
       </c>
       <c r="G10" t="n">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7776041666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3345656303396852</v>
+        <v>0.09676343990790283</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3345656303396852</v>
+        <v>0.1451451598618543</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6908163265306122</v>
+        <v>0.6820566631689402</v>
       </c>
       <c r="L10" t="n">
-        <v>1.016945441861206e-06</v>
+        <v>3.88781034691992e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>2.033890883722412e-06</v>
+        <v>7.775620693839841e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8746770025839793</v>
+        <v>0.8397932816537468</v>
       </c>
       <c r="O10" t="n">
-        <v>8.383971059840607e-19</v>
+        <v>1.13807230544921e-13</v>
       </c>
       <c r="P10" t="n">
-        <v>5.030382635904364e-18</v>
+        <v>3.414216916347631e-13</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7719498289623716</v>
+        <v>0.7527504342790967</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03816604437425253</v>
+        <v>0.1908055164647671</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04579925324910303</v>
+        <v>0.2289666197577206</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -425,623 +425,747 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>scenario</t>
+          <t>samples</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>samples</t>
+          <t>model</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>tp</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>fp</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>fp</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>fn</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>p_acc_fisher</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>p_acc_fisher</t>
+          <t>adj_p_acc_fisher</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>adj_p_acc_fisher</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>p_prec_fisher</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>p_prec_fisher</t>
+          <t>adj_p_prec_fisher</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>adj_p_prec_fisher</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>p_rec_fisher</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>p_rec_fisher</t>
+          <t>adj_p_rec_fisher</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>adj_p_rec_fisher</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>p_f1_fisher</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>p_f1_fisher</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
           <t>adj_p_f1_fisher</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>1920</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>GPT-4o base</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>558</v>
+      </c>
       <c r="D2" t="n">
-        <v>548</v>
+        <v>1072</v>
       </c>
       <c r="E2" t="n">
-        <v>1072</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
-        <v>226</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.84375</v>
-      </c>
+        <v>0.8489583333333334</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0.8810289389067524</v>
-      </c>
+      <c r="J2" t="n">
+        <v>0.8829113924050633</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>0.7080103359173127</v>
-      </c>
+      <c r="M2" t="n">
+        <v>0.7209302325581395</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>0.7851002865329513</v>
-      </c>
+      <c r="P2" t="n">
+        <v>0.7937411095305832</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
         <v>1920</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>GPT-4o FT</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>675</v>
+      </c>
       <c r="D3" t="n">
-        <v>674</v>
+        <v>1096</v>
       </c>
       <c r="E3" t="n">
-        <v>1096</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>0.9223958333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>0.921875</v>
+        <v>8.404632239514041e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>4.792162101787747e-14</v>
+        <v>2.916821778099137e-12</v>
       </c>
       <c r="J3" t="n">
-        <v>2.875297261072648e-13</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="K3" t="n">
-        <v>0.930939226519337</v>
+        <v>0.002440470676836155</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001766624481823072</v>
+        <v>0.003137748013075057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002119949378187686</v>
+        <v>0.8720930232558139</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8708010335917312</v>
+        <v>1.440569968418512e-13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.492797424219431e-15</v>
+        <v>4.321709905255536e-13</v>
       </c>
       <c r="P3" t="n">
-        <v>2.095678454531659e-14</v>
+        <v>0.9006004002668444</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8998664886515354</v>
+        <v>8.15677261988924e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.262293664965574e-17</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7.573761989793447e-17</v>
+        <v>3.670547678950158e-15</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="n">
         <v>1920</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GPT-4o FT+QSP</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>655</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F4" t="n">
+        <v>119</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8880208333333334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0004022592275305259</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0006033888412957888</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8721704394141145</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5657347799985153</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5657347799985153</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8462532299741602</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.558066354455247e-09</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.755649297524305e-09</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.859016393442623</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.175658330149893e-06</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.763487495224839e-06</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>GPT-4o QSP</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>625</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="C5" t="n">
+        <v>637</v>
+      </c>
+      <c r="D5" t="n">
         <v>1013</v>
       </c>
-      <c r="F4" t="n">
+      <c r="E5" t="n">
         <v>133</v>
       </c>
-      <c r="G4" t="n">
-        <v>149</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.853125</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.4442744244051946</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4442744244051946</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8245382585751979</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.003920867650364704</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.003920867650364704</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8074935400516796</v>
-      </c>
-      <c r="O4" t="n">
-        <v>6.178810321821877e-06</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.235762064364375e-05</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8159268929503917</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.03710235356968906</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.05565353035453359</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="F5" t="n">
+        <v>137</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.859375</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3850039281989391</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3850039281989391</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8272727272727273</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.003969652433621492</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.004465858987824178</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8229974160206718</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.138476242948483e-06</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.143169584378346e-06</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8251295336787564</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.03068252932058291</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.03944896626932089</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>1920</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Llama3.1-70B base</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="C6" t="n">
+        <v>562</v>
+      </c>
+      <c r="D6" t="n">
+        <v>967</v>
+      </c>
+      <c r="E6" t="n">
+        <v>179</v>
+      </c>
+      <c r="F6" t="n">
+        <v>212</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7963541666666667</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.7584345479082322</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0.7260981912144703</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0.7419141914191421</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>555</v>
       </c>
-      <c r="E5" t="n">
-        <v>967</v>
-      </c>
-      <c r="F5" t="n">
-        <v>179</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="D7" t="n">
+        <v>1122</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
         <v>219</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.7927083333333333</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0.7561307901907357</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="G7" t="n">
+        <v>0.8734375</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.42390538227345e-10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.563029688092209e-10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9585492227979274</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.805572348240029e-26</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.262507556708013e-25</v>
+      </c>
+      <c r="M7" t="n">
         <v>0.7170542635658915</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>0.7360742705570293</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="N7" t="n">
+        <v>0.7337082379418016</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7337082379418016</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8203991130820399</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.269898750350785e-07</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7.685817750631412e-07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>1920</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B FT</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>553</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1122</v>
-      </c>
-      <c r="F6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G6" t="n">
-        <v>221</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8723958333333334</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.249473635866948e-11</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8.498947271733896e-11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.9584055459272097</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.362265031491502e-26</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8.173590188949014e-26</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.7144702842377261</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.9550681075602224</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.9550681075602224</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.8186528497409327</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.439926366220674e-07</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.879852732441348e-07</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT+QSP</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>640</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1051</v>
+      </c>
+      <c r="E8" t="n">
+        <v>95</v>
+      </c>
+      <c r="F8" t="n">
+        <v>134</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8807291666666667</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.296365234710728e-12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.916821778099137e-12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8707482993197279</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.329710863277249e-08</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.491849442373809e-08</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8268733850129198</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.444687454516491e-06</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.143169584378346e-06</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8482438701126574</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.517457994292969e-13</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.016428048715918e-12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>1920</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Llama3.1-70B QSP</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>627</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="C9" t="n">
+        <v>640</v>
+      </c>
+      <c r="D9" t="n">
         <v>1051</v>
       </c>
-      <c r="F7" t="n">
+      <c r="E9" t="n">
         <v>95</v>
       </c>
-      <c r="G7" t="n">
-        <v>147</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.8739583333333333</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.592234122283897e-11</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.776702366851691e-11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.868421052631579</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4.679050960720545e-08</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.403715288216164e-07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.810077519379845</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.070535434355803e-05</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.105803151533705e-05</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8382352941176471</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7.823476059017284e-12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.347042817705185e-11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="F9" t="n">
+        <v>134</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8807291666666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.296365234710728e-12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.916821778099137e-12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8707482993197279</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.329710863277249e-08</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.491849442373809e-08</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8268733850129198</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.444687454516491e-06</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.143169584378346e-06</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8482438701126574</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.517457994292969e-13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.016428048715918e-12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>1920</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Llama3.1-8B base</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>525</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="C10" t="n">
+        <v>529</v>
+      </c>
+      <c r="D10" t="n">
         <v>1011</v>
       </c>
-      <c r="F8" t="n">
+      <c r="E10" t="n">
         <v>135</v>
       </c>
-      <c r="G8" t="n">
-        <v>249</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0.7954545454545454</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0.6782945736434108</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>0.7322175732217573</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="F10" t="n">
+        <v>245</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8020833333333334</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.7966867469879518</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0.6834625322997416</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0.7357440890125175</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>1920</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Llama3.1-8B FT</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>474</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C11" t="n">
+        <v>475</v>
+      </c>
+      <c r="D11" t="n">
         <v>1092</v>
       </c>
-      <c r="F9" t="n">
+      <c r="E11" t="n">
         <v>54</v>
       </c>
-      <c r="G9" t="n">
-        <v>300</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.815625</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.2349289652853259</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.281914758342391</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8977272727272727</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.433359763333451e-06</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.150039645000177e-06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6124031007751938</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.007871184960464721</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.009445421952557665</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.7281105990783411</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.8293084478898946</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.8293084478898946</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="F11" t="n">
+        <v>299</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8161458333333333</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2856873612257596</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3213982813789795</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8979206049149339</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.496555999356245e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.244833999034367e-06</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6136950904392765</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.004756645405541658</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.005351226081234365</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7290867229470454</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6976032440857345</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6976032440857345</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>1920</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT+QSP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>273</v>
+      </c>
+      <c r="D12" t="n">
+        <v>876</v>
+      </c>
+      <c r="E12" t="n">
+        <v>270</v>
+      </c>
+      <c r="F12" t="n">
+        <v>501</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5984375</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.460948651837427e-43</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.314853786653684e-42</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5027624309392266</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.054053019471593e-27</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.648647717524434e-26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3527131782945737</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.602474577166616e-39</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.242227119449955e-38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4145785876993166</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.303175823512285e-66</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.972858241161056e-65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Llama3.1-8B QSP</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>650</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="C13" t="n">
+        <v>665</v>
+      </c>
+      <c r="D13" t="n">
         <v>843</v>
       </c>
-      <c r="F10" t="n">
+      <c r="E13" t="n">
         <v>303</v>
       </c>
-      <c r="G10" t="n">
-        <v>124</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7776041666666667</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.09676343990790283</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.1451451598618543</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.6820566631689402</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3.88781034691992e-07</v>
-      </c>
-      <c r="M10" t="n">
-        <v>7.775620693839841e-07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.8397932816537468</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.13807230544921e-13</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.414216916347631e-13</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.7527504342790967</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1908055164647671</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.2289666197577206</v>
+      <c r="F13" t="n">
+        <v>109</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7854166666666667</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2162954632066621</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2780941669799942</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6869834710743802</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.312656571833097e-07</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.316278182929957e-06</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.8591731266149871</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.565206832669615e-16</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7.043430747013267e-16</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7634902411021816</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.07648927002644899</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.08605042877975512</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D2" t="n">
         <v>1072</v>
@@ -539,25 +539,25 @@
         <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8484375</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8829113924050633</v>
+        <v>0.8827258320126783</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7209302325581395</v>
+        <v>0.7196382428940569</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.7937411095305832</v>
+        <v>0.79288256227758</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -587,37 +587,37 @@
         <v>0.9223958333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>8.404632239514041e-13</v>
+        <v>6.069589665629366e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>2.916821778099137e-12</v>
+        <v>2.186628183045335e-12</v>
       </c>
       <c r="J3" t="n">
         <v>0.9310344827586207</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002440470676836155</v>
+        <v>0.002426031006193731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003137748013075057</v>
+        <v>0.003119182722249082</v>
       </c>
       <c r="M3" t="n">
         <v>0.8720930232558139</v>
       </c>
       <c r="N3" t="n">
-        <v>1.440569968418512e-13</v>
+        <v>9.458461699728301e-14</v>
       </c>
       <c r="O3" t="n">
-        <v>4.321709905255536e-13</v>
+        <v>2.83753850991849e-13</v>
       </c>
       <c r="P3" t="n">
         <v>0.9006004002668444</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.15677261988924e-16</v>
+        <v>5.54835348388866e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>3.670547678950158e-15</v>
+        <v>2.496759067749897e-15</v>
       </c>
     </row>
     <row r="4">
@@ -645,37 +645,37 @@
         <v>0.8880208333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004022592275305259</v>
+        <v>0.0003389708460945903</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006033888412957888</v>
+        <v>0.0005084562691418855</v>
       </c>
       <c r="J4" t="n">
         <v>0.8721704394141145</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5657347799985153</v>
+        <v>0.5659527810251433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5657347799985153</v>
+        <v>0.5659527810251433</v>
       </c>
       <c r="M4" t="n">
         <v>0.8462532299741602</v>
       </c>
       <c r="N4" t="n">
-        <v>2.558066354455247e-09</v>
+        <v>1.812472495962926e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.755649297524305e-09</v>
+        <v>4.078063115916584e-09</v>
       </c>
       <c r="P4" t="n">
         <v>0.859016393442623</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.175658330149893e-06</v>
+        <v>2.522813425422843e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.763487495224839e-06</v>
+        <v>3.784220138134265e-06</v>
       </c>
     </row>
     <row r="5">
@@ -703,37 +703,37 @@
         <v>0.859375</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3850039281989391</v>
+        <v>0.3608392330238829</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3850039281989391</v>
+        <v>0.3608392330238829</v>
       </c>
       <c r="J5" t="n">
         <v>0.8272727272727273</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003969652433621492</v>
+        <v>0.003975819319238917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004465858987824178</v>
+        <v>0.004472796734143782</v>
       </c>
       <c r="M5" t="n">
         <v>0.8229974160206718</v>
       </c>
       <c r="N5" t="n">
-        <v>2.138476242948483e-06</v>
+        <v>1.617198562650344e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>3.143169584378346e-06</v>
+        <v>2.376692341501569e-06</v>
       </c>
       <c r="P5" t="n">
         <v>0.8251295336787564</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03068252932058291</v>
+        <v>0.02726955352422656</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03944896626932089</v>
+        <v>0.03506085453114843</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D6" t="n">
         <v>967</v>
@@ -755,25 +755,25 @@
         <v>179</v>
       </c>
       <c r="F6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7963541666666667</v>
+        <v>0.7958333333333333</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.7584345479082322</v>
+        <v>0.7581081081081081</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.7260981912144703</v>
+        <v>0.7248062015503876</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.7419141914191421</v>
+        <v>0.7410832232496698</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -803,37 +803,37 @@
         <v>0.8734375</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42390538227345e-10</v>
+        <v>1.095706707542787e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>2.563029688092209e-10</v>
+        <v>1.972272073577017e-10</v>
       </c>
       <c r="J7" t="n">
         <v>0.9585492227979274</v>
       </c>
       <c r="K7" t="n">
-        <v>2.805572348240029e-26</v>
+        <v>2.709161331430057e-26</v>
       </c>
       <c r="L7" t="n">
-        <v>1.262507556708013e-25</v>
+        <v>1.219122599143526e-25</v>
       </c>
       <c r="M7" t="n">
         <v>0.7170542635658915</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7337082379418016</v>
+        <v>0.7769507172744308</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7337082379418016</v>
+        <v>0.7769507172744308</v>
       </c>
       <c r="P7" t="n">
         <v>0.8203991130820399</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.269898750350785e-07</v>
+        <v>3.398292581347678e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>7.685817750631412e-07</v>
+        <v>6.116926646425819e-07</v>
       </c>
     </row>
     <row r="8">
@@ -861,37 +861,37 @@
         <v>0.8807291666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>1.296365234710728e-12</v>
+        <v>9.718347480201489e-13</v>
       </c>
       <c r="I8" t="n">
-        <v>2.916821778099137e-12</v>
+        <v>2.186628183045335e-12</v>
       </c>
       <c r="J8" t="n">
         <v>0.8707482993197279</v>
       </c>
       <c r="K8" t="n">
-        <v>3.329710863277249e-08</v>
+        <v>2.38589013261989e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.491849442373809e-08</v>
+        <v>5.368252798394752e-08</v>
       </c>
       <c r="M8" t="n">
         <v>0.8268733850129198</v>
       </c>
       <c r="N8" t="n">
-        <v>2.444687454516491e-06</v>
+        <v>1.848538487834554e-06</v>
       </c>
       <c r="O8" t="n">
-        <v>3.143169584378346e-06</v>
+        <v>2.376692341501569e-06</v>
       </c>
       <c r="P8" t="n">
         <v>0.8482438701126574</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.517457994292969e-13</v>
+        <v>3.315586640494964e-13</v>
       </c>
       <c r="R8" t="n">
-        <v>1.016428048715918e-12</v>
+        <v>7.460069941113669e-13</v>
       </c>
     </row>
     <row r="9">
@@ -919,37 +919,37 @@
         <v>0.8807291666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>1.296365234710728e-12</v>
+        <v>9.718347480201489e-13</v>
       </c>
       <c r="I9" t="n">
-        <v>2.916821778099137e-12</v>
+        <v>2.186628183045335e-12</v>
       </c>
       <c r="J9" t="n">
         <v>0.8707482993197279</v>
       </c>
       <c r="K9" t="n">
-        <v>3.329710863277249e-08</v>
+        <v>2.38589013261989e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.491849442373809e-08</v>
+        <v>5.368252798394752e-08</v>
       </c>
       <c r="M9" t="n">
         <v>0.8268733850129198</v>
       </c>
       <c r="N9" t="n">
-        <v>2.444687454516491e-06</v>
+        <v>1.848538487834554e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>3.143169584378346e-06</v>
+        <v>2.376692341501569e-06</v>
       </c>
       <c r="P9" t="n">
         <v>0.8482438701126574</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.517457994292969e-13</v>
+        <v>3.315586640494964e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>1.016428048715918e-12</v>
+        <v>7.460069941113669e-13</v>
       </c>
     </row>
     <row r="10">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D10" t="n">
         <v>1011</v>
@@ -971,25 +971,25 @@
         <v>135</v>
       </c>
       <c r="F10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.8015625</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.7966867469879518</v>
+        <v>0.7963800904977375</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0.6834625322997416</v>
+        <v>0.6821705426356589</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.7357440890125175</v>
+        <v>0.7348643006263048</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1019,37 +1019,37 @@
         <v>0.8161458333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2856873612257596</v>
+        <v>0.2678086744554857</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3213982813789795</v>
+        <v>0.3012847587624214</v>
       </c>
       <c r="J11" t="n">
         <v>0.8979206049149339</v>
       </c>
       <c r="K11" t="n">
-        <v>1.496555999356245e-06</v>
+        <v>1.471950876532742e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>2.244833999034367e-06</v>
+        <v>2.207926314799113e-06</v>
       </c>
       <c r="M11" t="n">
         <v>0.6136950904392765</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004756645405541658</v>
+        <v>0.005630241556060989</v>
       </c>
       <c r="O11" t="n">
-        <v>0.005351226081234365</v>
+        <v>0.006334021750568613</v>
       </c>
       <c r="P11" t="n">
         <v>0.7290867229470454</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6976032440857345</v>
+        <v>0.7624161049031354</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6976032440857345</v>
+        <v>0.7624161049031354</v>
       </c>
     </row>
     <row r="12">
@@ -1077,37 +1077,37 @@
         <v>0.5984375</v>
       </c>
       <c r="H12" t="n">
-        <v>1.460948651837427e-43</v>
+        <v>2.534618559489311e-43</v>
       </c>
       <c r="I12" t="n">
-        <v>1.314853786653684e-42</v>
+        <v>2.281156703540379e-42</v>
       </c>
       <c r="J12" t="n">
         <v>0.5027624309392266</v>
       </c>
       <c r="K12" t="n">
-        <v>4.054053019471593e-27</v>
+        <v>7.032681875812243e-27</v>
       </c>
       <c r="L12" t="n">
-        <v>3.648647717524434e-26</v>
+        <v>6.329413688231019e-26</v>
       </c>
       <c r="M12" t="n">
         <v>0.3527131782945737</v>
       </c>
       <c r="N12" t="n">
-        <v>3.602474577166616e-39</v>
+        <v>7.229901991227382e-39</v>
       </c>
       <c r="O12" t="n">
-        <v>3.242227119449955e-38</v>
+        <v>6.506911792104644e-38</v>
       </c>
       <c r="P12" t="n">
         <v>0.4145785876993166</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.303175823512285e-66</v>
+        <v>7.007252180157548e-66</v>
       </c>
       <c r="R12" t="n">
-        <v>2.972858241161056e-65</v>
+        <v>6.306526962141794e-65</v>
       </c>
     </row>
     <row r="13">
@@ -1135,37 +1135,37 @@
         <v>0.7854166666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2162954632066621</v>
+        <v>0.2317015170409039</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2780941669799942</v>
+        <v>0.2979019504811622</v>
       </c>
       <c r="J13" t="n">
         <v>0.6869834710743802</v>
       </c>
       <c r="K13" t="n">
-        <v>7.312656571833097e-07</v>
+        <v>9.413308698768831e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>1.316278182929957e-06</v>
+        <v>1.69439556577839e-06</v>
       </c>
       <c r="M13" t="n">
         <v>0.8591731266149871</v>
       </c>
       <c r="N13" t="n">
-        <v>1.565206832669615e-16</v>
+        <v>9.976022558663979e-17</v>
       </c>
       <c r="O13" t="n">
-        <v>7.043430747013267e-16</v>
+        <v>4.489210151398791e-16</v>
       </c>
       <c r="P13" t="n">
         <v>0.7634902411021816</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07648927002644899</v>
+        <v>0.06402280147104748</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08605042877975512</v>
+        <v>0.07202565165492841</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -590,7 +590,7 @@
         <v>6.069589665629366e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>2.186628183045335e-12</v>
+        <v>2.915504244060446e-12</v>
       </c>
       <c r="J3" t="n">
         <v>0.9310344827586207</v>
@@ -608,7 +608,7 @@
         <v>9.458461699728301e-14</v>
       </c>
       <c r="O3" t="n">
-        <v>2.83753850991849e-13</v>
+        <v>4.256307764877735e-13</v>
       </c>
       <c r="P3" t="n">
         <v>0.9006004002668444</v>
@@ -617,7 +617,7 @@
         <v>5.54835348388866e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>2.496759067749897e-15</v>
+        <v>4.993518135499794e-15</v>
       </c>
     </row>
     <row r="4">
@@ -666,7 +666,7 @@
         <v>1.812472495962926e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.078063115916584e-09</v>
+        <v>5.437417487888779e-09</v>
       </c>
       <c r="P4" t="n">
         <v>0.859016393442623</v>
@@ -724,7 +724,7 @@
         <v>1.617198562650344e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.376692341501569e-06</v>
+        <v>2.77280773175183e-06</v>
       </c>
       <c r="P5" t="n">
         <v>0.8251295336787564</v>
@@ -806,7 +806,7 @@
         <v>1.095706707542787e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>1.972272073577017e-10</v>
+        <v>2.465340091971271e-10</v>
       </c>
       <c r="J7" t="n">
         <v>0.9585492227979274</v>
@@ -815,7 +815,7 @@
         <v>2.709161331430057e-26</v>
       </c>
       <c r="L7" t="n">
-        <v>1.219122599143526e-25</v>
+        <v>2.438245198287052e-25</v>
       </c>
       <c r="M7" t="n">
         <v>0.7170542635658915</v>
@@ -864,7 +864,7 @@
         <v>9.718347480201489e-13</v>
       </c>
       <c r="I8" t="n">
-        <v>2.186628183045335e-12</v>
+        <v>2.915504244060446e-12</v>
       </c>
       <c r="J8" t="n">
         <v>0.8707482993197279</v>
@@ -873,7 +873,7 @@
         <v>2.38589013261989e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.368252798394752e-08</v>
+        <v>7.15767039785967e-08</v>
       </c>
       <c r="M8" t="n">
         <v>0.8268733850129198</v>
@@ -882,7 +882,7 @@
         <v>1.848538487834554e-06</v>
       </c>
       <c r="O8" t="n">
-        <v>2.376692341501569e-06</v>
+        <v>2.77280773175183e-06</v>
       </c>
       <c r="P8" t="n">
         <v>0.8482438701126574</v>
@@ -891,7 +891,7 @@
         <v>3.315586640494964e-13</v>
       </c>
       <c r="R8" t="n">
-        <v>7.460069941113669e-13</v>
+        <v>9.946759921484891e-13</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>9.718347480201489e-13</v>
       </c>
       <c r="I9" t="n">
-        <v>2.186628183045335e-12</v>
+        <v>2.915504244060446e-12</v>
       </c>
       <c r="J9" t="n">
         <v>0.8707482993197279</v>
@@ -931,7 +931,7 @@
         <v>2.38589013261989e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.368252798394752e-08</v>
+        <v>7.15767039785967e-08</v>
       </c>
       <c r="M9" t="n">
         <v>0.8268733850129198</v>
@@ -940,7 +940,7 @@
         <v>1.848538487834554e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>2.376692341501569e-06</v>
+        <v>2.77280773175183e-06</v>
       </c>
       <c r="P9" t="n">
         <v>0.8482438701126574</v>
@@ -949,7 +949,7 @@
         <v>3.315586640494964e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>7.460069941113669e-13</v>
+        <v>9.946759921484891e-13</v>
       </c>
     </row>
     <row r="10">
@@ -1062,52 +1062,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>273</v>
+        <v>452</v>
       </c>
       <c r="D12" t="n">
-        <v>876</v>
+        <v>926</v>
       </c>
       <c r="E12" t="n">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="F12" t="n">
-        <v>501</v>
+        <v>322</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5984375</v>
+        <v>0.7177083333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>2.534618559489311e-43</v>
+        <v>1.411545721776998e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>2.281156703540379e-42</v>
+        <v>2.540782299198596e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5027624309392266</v>
+        <v>0.6726190476190477</v>
       </c>
       <c r="K12" t="n">
-        <v>7.032681875812243e-27</v>
+        <v>3.480883508051594e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>6.329413688231019e-26</v>
+        <v>7.831987893116087e-07</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3527131782945737</v>
+        <v>0.5839793281653747</v>
       </c>
       <c r="N12" t="n">
-        <v>7.229901991227382e-39</v>
+        <v>7.51982130596092e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>6.506911792104644e-38</v>
+        <v>9.668341679092611e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4145785876993166</v>
+        <v>0.6251728907330567</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.007252180157548e-66</v>
+        <v>2.701208700346179e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>6.306526962141794e-65</v>
+        <v>6.077719575778903e-10</v>
       </c>
     </row>
     <row r="13">
@@ -1156,7 +1156,7 @@
         <v>9.976022558663979e-17</v>
       </c>
       <c r="O13" t="n">
-        <v>4.489210151398791e-16</v>
+        <v>8.978420302797581e-16</v>
       </c>
       <c r="P13" t="n">
         <v>0.7634902411021816</v>

--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -590,7 +590,7 @@
         <v>6.069589665629366e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>2.915504244060446e-12</v>
+        <v>4.37325636609067e-12</v>
       </c>
       <c r="J3" t="n">
         <v>0.9310344827586207</v>
@@ -675,7 +675,7 @@
         <v>2.522813425422843e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>3.784220138134265e-06</v>
+        <v>4.541064165761117e-06</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>1.617198562650344e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.77280773175183e-06</v>
+        <v>3.327369278102196e-06</v>
       </c>
       <c r="P5" t="n">
         <v>0.8251295336787564</v>
@@ -806,7 +806,7 @@
         <v>1.095706707542787e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>2.465340091971271e-10</v>
+        <v>3.287120122628362e-10</v>
       </c>
       <c r="J7" t="n">
         <v>0.9585492227979274</v>
@@ -833,7 +833,7 @@
         <v>3.398292581347678e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>6.116926646425819e-07</v>
+        <v>7.646158308032275e-07</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>640</v>
+        <v>512</v>
       </c>
       <c r="D8" t="n">
-        <v>1051</v>
+        <v>1118</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8807291666666667</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>9.718347480201489e-13</v>
+        <v>1.947119021625719e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.915504244060446e-12</v>
+        <v>3.504814238926294e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.9481481481481482</v>
       </c>
       <c r="K8" t="n">
-        <v>2.38589013261989e-08</v>
+        <v>5.797840713000428e-22</v>
       </c>
       <c r="L8" t="n">
-        <v>7.15767039785967e-08</v>
+        <v>2.609028320850193e-21</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8268733850129198</v>
+        <v>0.6614987080103359</v>
       </c>
       <c r="N8" t="n">
-        <v>1.848538487834554e-06</v>
+        <v>0.008126011797106713</v>
       </c>
       <c r="O8" t="n">
-        <v>2.77280773175183e-06</v>
+        <v>0.009141763271745052</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8482438701126574</v>
+        <v>0.7792998477929984</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.315586640494964e-13</v>
+        <v>0.01947727682012174</v>
       </c>
       <c r="R8" t="n">
-        <v>9.946759921484891e-13</v>
+        <v>0.02921591523018261</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>9.718347480201489e-13</v>
       </c>
       <c r="I9" t="n">
-        <v>2.915504244060446e-12</v>
+        <v>4.37325636609067e-12</v>
       </c>
       <c r="J9" t="n">
         <v>0.8707482993197279</v>
@@ -940,7 +940,7 @@
         <v>1.848538487834554e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>2.77280773175183e-06</v>
+        <v>3.327369278102196e-06</v>
       </c>
       <c r="P9" t="n">
         <v>0.8482438701126574</v>
@@ -949,7 +949,7 @@
         <v>3.315586640494964e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>9.946759921484891e-13</v>
+        <v>1.492013988222734e-12</v>
       </c>
     </row>
     <row r="10">
@@ -1040,7 +1040,7 @@
         <v>0.005630241556060989</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006334021750568613</v>
+        <v>0.007238882000649843</v>
       </c>
       <c r="P11" t="n">
         <v>0.7290867229470454</v>
@@ -1080,7 +1080,7 @@
         <v>1.411545721776998e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>2.540782299198596e-09</v>
+        <v>3.175977873998246e-09</v>
       </c>
       <c r="J12" t="n">
         <v>0.6726190476190477</v>
@@ -1098,7 +1098,7 @@
         <v>7.51982130596092e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>9.668341679092611e-05</v>
+        <v>0.0001127973195894138</v>
       </c>
       <c r="P12" t="n">
         <v>0.6251728907330567</v>
@@ -1107,7 +1107,7 @@
         <v>2.701208700346179e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>6.077719575778903e-10</v>
+        <v>8.103626101038537e-10</v>
       </c>
     </row>
     <row r="13">

--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -530,34 +530,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D2" t="n">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E2" t="n">
         <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8484375</v>
+        <v>0.8510416666666667</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8827258320126783</v>
+        <v>0.8829113924050633</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7196382428940569</v>
+        <v>0.7246753246753247</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.79288256227758</v>
+        <v>0.7960057061340942</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D3" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9223958333333333</v>
+        <v>0.925</v>
       </c>
       <c r="H3" t="n">
-        <v>6.069589665629366e-13</v>
+        <v>3.480273739794593e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>4.37325636609067e-12</v>
+        <v>2.134636765001951e-12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.931129476584022</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002426031006193731</v>
+        <v>0.002429460245091898</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003119182722249082</v>
+        <v>0.003123591743689584</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8720930232558139</v>
+        <v>0.8779220779220779</v>
       </c>
       <c r="N3" t="n">
-        <v>9.458461699728301e-14</v>
+        <v>4.395027394060365e-14</v>
       </c>
       <c r="O3" t="n">
-        <v>4.256307764877735e-13</v>
+        <v>1.977762327327164e-13</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9006004002668444</v>
+        <v>0.9037433155080213</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.54835348388866e-16</v>
+        <v>2.87554653119588e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>4.993518135499794e-15</v>
+        <v>2.587991878076292e-15</v>
       </c>
     </row>
     <row r="4">
@@ -630,52 +630,52 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D4" t="n">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="E4" t="n">
         <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8880208333333334</v>
+        <v>0.890625</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003389708460945903</v>
+        <v>0.0003011489280871884</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005084562691418855</v>
+        <v>0.0004517233921307826</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8721704394141145</v>
+        <v>0.8723404255319149</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5659527810251433</v>
+        <v>0.5659509913169587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5659527810251433</v>
+        <v>0.5659509913169587</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8462532299741602</v>
+        <v>0.8519480519480519</v>
       </c>
       <c r="N4" t="n">
-        <v>1.812472495962926e-09</v>
+        <v>1.151348998394792e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.437417487888779e-09</v>
+        <v>3.454046995184377e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>0.859016393442623</v>
+        <v>0.8620236530880421</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.522813425422843e-06</v>
+        <v>2.11133466281812e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.541064165761117e-06</v>
+        <v>3.800402393072615e-06</v>
       </c>
     </row>
     <row r="5">
@@ -691,49 +691,49 @@
         <v>637</v>
       </c>
       <c r="D5" t="n">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="E5" t="n">
         <v>133</v>
       </c>
       <c r="F5" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G5" t="n">
-        <v>0.859375</v>
+        <v>0.8614583333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3608392330238829</v>
+        <v>0.3821612428226822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3608392330238829</v>
+        <v>0.3821612428226822</v>
       </c>
       <c r="J5" t="n">
         <v>0.8272727272727273</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003975819319238917</v>
+        <v>0.003969652433621492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004472796734143782</v>
+        <v>0.004465858987824178</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8229974160206718</v>
+        <v>0.8272727272727273</v>
       </c>
       <c r="N5" t="n">
-        <v>1.617198562650344e-06</v>
+        <v>1.7278852770407e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>3.327369278102196e-06</v>
+        <v>3.11019349867326e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8251295336787564</v>
+        <v>0.8272727272727273</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02726955352422656</v>
+        <v>0.03332883988616975</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03506085453114843</v>
+        <v>0.04285136556793253</v>
       </c>
     </row>
     <row r="6">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D6" t="n">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E6" t="n">
         <v>179</v>
       </c>
       <c r="F6" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7958333333333333</v>
+        <v>0.7984375</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.7581081081081081</v>
+        <v>0.7584345479082322</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.7248062015503876</v>
+        <v>0.7298701298701299</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.7410832232496698</v>
+        <v>0.743878226340172</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -788,52 +788,52 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D7" t="n">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8734375</v>
+        <v>0.8760416666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>1.095706707542787e-10</v>
+        <v>8.286796079495435e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>3.287120122628362e-10</v>
+        <v>2.486038823848631e-10</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9585492227979274</v>
+        <v>0.9586206896551724</v>
       </c>
       <c r="K7" t="n">
-        <v>2.709161331430057e-26</v>
+        <v>2.732497690299795e-26</v>
       </c>
       <c r="L7" t="n">
-        <v>2.438245198287052e-25</v>
+        <v>2.459247921269816e-25</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7170542635658915</v>
+        <v>0.7220779220779221</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7769507172744308</v>
+        <v>0.7751587958077072</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7769507172744308</v>
+        <v>0.7751587958077072</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8203991130820399</v>
+        <v>0.8237037037037038</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.398292581347678e-07</v>
+        <v>2.303507459312819e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>7.646158308032275e-07</v>
+        <v>5.182891783453841e-07</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D8" t="n">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="E8" t="n">
         <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8489583333333334</v>
+        <v>0.8515625</v>
       </c>
       <c r="H8" t="n">
-        <v>1.947119021625719e-05</v>
+        <v>1.739524855405292e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.504814238926294e-05</v>
+        <v>3.131144739729526e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9481481481481482</v>
+        <v>0.9482439926062847</v>
       </c>
       <c r="K8" t="n">
-        <v>5.797840713000428e-22</v>
+        <v>5.762592220825834e-22</v>
       </c>
       <c r="L8" t="n">
-        <v>2.609028320850193e-21</v>
+        <v>2.593166499371625e-21</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6614987080103359</v>
+        <v>0.6662337662337663</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008126011797106713</v>
+        <v>0.007681379759841662</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009141763271745052</v>
+        <v>0.00864155222982187</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7792998477929984</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01947727682012174</v>
+        <v>0.01673033361057287</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02921591523018261</v>
+        <v>0.0250955004158593</v>
       </c>
     </row>
     <row r="9">
@@ -904,52 +904,52 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D9" t="n">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="E9" t="n">
         <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8807291666666667</v>
+        <v>0.8838541666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>9.718347480201489e-13</v>
+        <v>4.743637255559891e-13</v>
       </c>
       <c r="I9" t="n">
-        <v>4.37325636609067e-12</v>
+        <v>2.134636765001951e-12</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.8710990502035278</v>
       </c>
       <c r="K9" t="n">
-        <v>2.38589013261989e-08</v>
+        <v>2.352136151869484e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.15767039785967e-08</v>
+        <v>7.056408455608454e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8268733850129198</v>
+        <v>0.8337662337662337</v>
       </c>
       <c r="N9" t="n">
-        <v>1.848538487834554e-06</v>
+        <v>9.994541592869413e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>3.327369278102196e-06</v>
+        <v>2.248771858395618e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8482438701126574</v>
+        <v>0.8520238885202388</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.315586640494964e-13</v>
+        <v>1.17559531502712e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>1.492013988222734e-12</v>
+        <v>5.290178917622042e-13</v>
       </c>
     </row>
     <row r="10">
@@ -965,16 +965,16 @@
         <v>528</v>
       </c>
       <c r="D10" t="n">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="E10" t="n">
         <v>135</v>
       </c>
       <c r="F10" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8015625</v>
+        <v>0.8036458333333333</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -984,12 +984,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0.6821705426356589</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.7348643006263048</v>
+        <v>0.7369155617585484</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1007,22 +1007,22 @@
         <v>475</v>
       </c>
       <c r="D11" t="n">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E11" t="n">
         <v>54</v>
       </c>
       <c r="F11" t="n">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8161458333333333</v>
+        <v>0.8182291666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2678086744554857</v>
+        <v>0.26580261883432</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3012847587624214</v>
+        <v>0.2990279461886101</v>
       </c>
       <c r="J11" t="n">
         <v>0.8979206049149339</v>
@@ -1034,22 +1034,22 @@
         <v>2.207926314799113e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6136950904392765</v>
+        <v>0.6168831168831169</v>
       </c>
       <c r="N11" t="n">
-        <v>0.005630241556060989</v>
+        <v>0.005403417140068575</v>
       </c>
       <c r="O11" t="n">
-        <v>0.007238882000649843</v>
+        <v>0.006947250608659597</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7290867229470454</v>
+        <v>0.731331793687452</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7624161049031354</v>
+        <v>0.7615153072717027</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7624161049031354</v>
+        <v>0.7615153072717027</v>
       </c>
     </row>
     <row r="12">
@@ -1065,22 +1065,22 @@
         <v>452</v>
       </c>
       <c r="D12" t="n">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="E12" t="n">
         <v>220</v>
       </c>
       <c r="F12" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7177083333333333</v>
+        <v>0.7197916666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>1.411545721776998e-09</v>
+        <v>1.259536481908166e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>3.175977873998246e-09</v>
+        <v>2.833957084293373e-09</v>
       </c>
       <c r="J12" t="n">
         <v>0.6726190476190477</v>
@@ -1092,22 +1092,22 @@
         <v>7.831987893116087e-07</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5839793281653747</v>
+        <v>0.587012987012987</v>
       </c>
       <c r="N12" t="n">
-        <v>7.51982130596092e-05</v>
+        <v>6.973519209817601e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0001127973195894138</v>
+        <v>0.000104602788147264</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6251728907330567</v>
+        <v>0.6269070735090153</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.701208700346179e-10</v>
+        <v>2.387313754129081e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>8.103626101038537e-10</v>
+        <v>7.161941262387242e-10</v>
       </c>
     </row>
     <row r="13">
@@ -1123,22 +1123,22 @@
         <v>665</v>
       </c>
       <c r="D13" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="E13" t="n">
         <v>303</v>
       </c>
       <c r="F13" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.7875</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2317015170409039</v>
+        <v>0.2299481170978297</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2979019504811622</v>
+        <v>0.295647579125781</v>
       </c>
       <c r="J13" t="n">
         <v>0.6869834710743802</v>
@@ -1150,22 +1150,22 @@
         <v>1.69439556577839e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8591731266149871</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="N13" t="n">
-        <v>9.976022558663979e-17</v>
+        <v>5.159582950176259e-17</v>
       </c>
       <c r="O13" t="n">
-        <v>8.978420302797581e-16</v>
+        <v>4.643624655158633e-16</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7634902411021816</v>
+        <v>0.7652474108170311</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.06402280147104748</v>
+        <v>0.06895128089371601</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07202565165492841</v>
+        <v>0.07757019100543051</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_original120.xlsx
+++ b/eval/results/evaluation_metrics_fisher_original120.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D2" t="n">
         <v>1076</v>
@@ -539,25 +539,25 @@
         <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8510416666666667</v>
+        <v>0.8505208333333333</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8829113924050633</v>
+        <v>0.8827258320126783</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7246753246753247</v>
+        <v>0.7233766233766233</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.7960057061340942</v>
+        <v>0.7951463240542469</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D3" t="n">
         <v>1100</v>
@@ -581,43 +581,43 @@
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>0.925</v>
+        <v>0.9244791666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3.480273739794593e-13</v>
+        <v>3.898328466426899e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>2.134636765001951e-12</v>
+        <v>3.303054923647291e-12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.931129476584022</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002429460245091898</v>
+        <v>0.002426031006193731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003123591743689584</v>
+        <v>0.003119182722249082</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8779220779220779</v>
+        <v>0.8766233766233766</v>
       </c>
       <c r="N3" t="n">
-        <v>4.395027394060365e-14</v>
+        <v>5.107588530568728e-14</v>
       </c>
       <c r="O3" t="n">
-        <v>1.977762327327164e-13</v>
+        <v>2.298414838755928e-13</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9037433155080213</v>
+        <v>0.9030100334448159</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.87554653119588e-16</v>
+        <v>3.257250881274176e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>2.587991878076292e-15</v>
+        <v>2.931525793146759e-15</v>
       </c>
     </row>
     <row r="4">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D4" t="n">
         <v>1054</v>
@@ -639,43 +639,43 @@
         <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.890625</v>
+        <v>0.8901041666666667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0003011489280871884</v>
+        <v>0.0003084783794065122</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004517233921307826</v>
+        <v>0.0004627175691097683</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8723404255319149</v>
+        <v>0.8721704394141145</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5659509913169587</v>
+        <v>0.5659527810251433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5659509913169587</v>
+        <v>0.5659527810251433</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8519480519480519</v>
+        <v>0.8506493506493507</v>
       </c>
       <c r="N4" t="n">
-        <v>1.151348998394792e-09</v>
+        <v>1.257025172799433e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>3.454046995184377e-09</v>
+        <v>3.7710755183983e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8620236530880421</v>
+        <v>0.8612754766600921</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.11133466281812e-06</v>
+        <v>2.179894510951001e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>3.800402393072615e-06</v>
+        <v>3.923810119711802e-06</v>
       </c>
     </row>
     <row r="5">
@@ -703,37 +703,37 @@
         <v>0.8614583333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3821612428226822</v>
+        <v>0.3579737530505324</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3821612428226822</v>
+        <v>0.3579737530505324</v>
       </c>
       <c r="J5" t="n">
         <v>0.8272727272727273</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003969652433621492</v>
+        <v>0.003975819319238917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004465858987824178</v>
+        <v>0.004472796734143782</v>
       </c>
       <c r="M5" t="n">
         <v>0.8272727272727273</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7278852770407e-06</v>
+        <v>1.301241713644353e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>3.11019349867326e-06</v>
+        <v>2.668092296453636e-06</v>
       </c>
       <c r="P5" t="n">
         <v>0.8272727272727273</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03332883988616975</v>
+        <v>0.02645579193634775</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04285136556793253</v>
+        <v>0.03401458963244711</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D6" t="n">
         <v>971</v>
@@ -755,25 +755,25 @@
         <v>179</v>
       </c>
       <c r="F6" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7984375</v>
+        <v>0.7979166666666667</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.7584345479082322</v>
+        <v>0.7581081081081081</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.7298701298701299</v>
+        <v>0.7285714285714285</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.743878226340172</v>
+        <v>0.743046357615894</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -803,37 +803,37 @@
         <v>0.8760416666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>8.286796079495435e-11</v>
+        <v>6.350378591128118e-11</v>
       </c>
       <c r="I7" t="n">
-        <v>2.486038823848631e-10</v>
+        <v>1.905113577338435e-10</v>
       </c>
       <c r="J7" t="n">
         <v>0.9586206896551724</v>
       </c>
       <c r="K7" t="n">
-        <v>2.732497690299795e-26</v>
+        <v>2.675300252235912e-26</v>
       </c>
       <c r="L7" t="n">
-        <v>2.459247921269816e-25</v>
+        <v>2.407770227012321e-25</v>
       </c>
       <c r="M7" t="n">
         <v>0.7220779220779221</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7751587958077072</v>
+        <v>0.8193834240789742</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7751587958077072</v>
+        <v>0.8193834240789742</v>
       </c>
       <c r="P7" t="n">
         <v>0.8237037037037038</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.303507459312819e-07</v>
+        <v>1.817510964024131e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>5.182891783453841e-07</v>
+        <v>4.089399669054296e-07</v>
       </c>
     </row>
     <row r="8">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D8" t="n">
         <v>1122</v>
@@ -855,43 +855,43 @@
         <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8515625</v>
+        <v>0.8510416666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>1.739524855405292e-05</v>
+        <v>1.779693756782975e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.131144739729526e-05</v>
+        <v>3.203448762209354e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9482439926062847</v>
+        <v>0.9481481481481482</v>
       </c>
       <c r="K8" t="n">
-        <v>5.762592220825834e-22</v>
+        <v>5.797840713000428e-22</v>
       </c>
       <c r="L8" t="n">
-        <v>2.593166499371625e-21</v>
+        <v>2.609028320850193e-21</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6662337662337663</v>
+        <v>0.6649350649350649</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007681379759841662</v>
+        <v>0.007755977423752855</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00864155222982187</v>
+        <v>0.008725474601721961</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7816793893129771</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01673033361057287</v>
+        <v>0.01685523340923336</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0250955004158593</v>
+        <v>0.02528285011385004</v>
       </c>
     </row>
     <row r="9">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D9" t="n">
         <v>1055</v>
@@ -913,43 +913,43 @@
         <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8838541666666667</v>
+        <v>0.8828125</v>
       </c>
       <c r="H9" t="n">
-        <v>4.743637255559891e-13</v>
+        <v>7.340122052549535e-13</v>
       </c>
       <c r="I9" t="n">
-        <v>2.134636765001951e-12</v>
+        <v>3.303054923647291e-12</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8710990502035278</v>
+        <v>0.8707482993197279</v>
       </c>
       <c r="K9" t="n">
-        <v>2.352136151869484e-08</v>
+        <v>2.38589013261989e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.056408455608454e-08</v>
+        <v>7.15767039785967e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8337662337662337</v>
+        <v>0.8311688311688312</v>
       </c>
       <c r="N9" t="n">
-        <v>9.994541592869413e-07</v>
+        <v>1.482273498029798e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>2.248771858395618e-06</v>
+        <v>2.668092296453636e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8520238885202388</v>
+        <v>0.8504983388704319</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.17559531502712e-13</v>
+        <v>1.869011764229038e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>5.290178917622042e-13</v>
+        <v>8.410552939030669e-13</v>
       </c>
     </row>
     <row r="10">
